--- a/artfynd/A 51121-2022 artfynd.xlsx
+++ b/artfynd/A 51121-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134349539</v>
+        <v>134349616</v>
       </c>
       <c r="B2" t="n">
         <v>99181</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483155</v>
+        <v>483159</v>
       </c>
       <c r="R2" t="n">
-        <v>6845008</v>
+        <v>6844996</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134349616</v>
+        <v>134349187</v>
       </c>
       <c r="B3" t="n">
         <v>99181</v>
@@ -800,17 +800,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483159</v>
+        <v>483105</v>
       </c>
       <c r="R3" t="n">
-        <v>6844996</v>
+        <v>6845012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +878,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134349187</v>
+        <v>134349539</v>
       </c>
       <c r="B4" t="n">
         <v>99181</v>
@@ -897,26 +906,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483105</v>
+        <v>483155</v>
       </c>
       <c r="R4" t="n">
-        <v>6845012</v>
+        <v>6845008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134349278</v>
+        <v>134348872</v>
       </c>
       <c r="B7" t="n">
         <v>99181</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483128</v>
+        <v>483089</v>
       </c>
       <c r="R7" t="n">
-        <v>6845017</v>
+        <v>6844992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134348872</v>
+        <v>134349278</v>
       </c>
       <c r="B8" t="n">
         <v>99181</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483089</v>
+        <v>483128</v>
       </c>
       <c r="R8" t="n">
-        <v>6844992</v>
+        <v>6845017</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134349215</v>
+        <v>134349250</v>
       </c>
       <c r="B11" t="n">
         <v>99181</v>
@@ -1585,29 +1585,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483108</v>
+        <v>483121</v>
       </c>
       <c r="R11" t="n">
-        <v>6845021</v>
+        <v>6845025</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134349250</v>
+        <v>134349215</v>
       </c>
       <c r="B12" t="n">
         <v>99181</v>
@@ -1691,20 +1682,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483121</v>
+        <v>483108</v>
       </c>
       <c r="R12" t="n">
-        <v>6845025</v>
+        <v>6845021</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1954,32 +1954,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134349116</v>
+        <v>134348728</v>
       </c>
       <c r="B15" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483079</v>
+        <v>483141</v>
       </c>
       <c r="R15" t="n">
-        <v>6844999</v>
+        <v>6844968</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2025,6 +2025,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2051,32 +2056,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134348728</v>
+        <v>134349116</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2086,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483141</v>
+        <v>483079</v>
       </c>
       <c r="R16" t="n">
-        <v>6844968</v>
+        <v>6844999</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,11 +2127,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134349703</v>
+        <v>134349429</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>58107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2261,34 +2261,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>205976</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483195</v>
+        <v>483134</v>
       </c>
       <c r="R18" t="n">
-        <v>6844994</v>
+        <v>6844986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,10 +2352,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134349429</v>
+        <v>134349703</v>
       </c>
       <c r="B19" t="n">
-        <v>58107</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2358,39 +2363,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205976</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483134</v>
+        <v>483195</v>
       </c>
       <c r="R19" t="n">
-        <v>6844986</v>
+        <v>6844994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134349101</v>
+        <v>134349302</v>
       </c>
       <c r="B23" t="n">
         <v>99181</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483077</v>
+        <v>483126</v>
       </c>
       <c r="R23" t="n">
-        <v>6844998</v>
+        <v>6845005</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134349302</v>
+        <v>134349101</v>
       </c>
       <c r="B24" t="n">
         <v>99181</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483126</v>
+        <v>483077</v>
       </c>
       <c r="R24" t="n">
-        <v>6845005</v>
+        <v>6844998</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 51121-2022 artfynd.xlsx
+++ b/artfynd/A 51121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134349616</v>
+        <v>134349539</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483159</v>
+        <v>483155</v>
       </c>
       <c r="R2" t="n">
-        <v>6844996</v>
+        <v>6845008</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>134349187</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134349539</v>
+        <v>134349616</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483155</v>
+        <v>483159</v>
       </c>
       <c r="R4" t="n">
-        <v>6845008</v>
+        <v>6844996</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
         <v>134350051</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>134349953</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134348872</v>
+        <v>134349278</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483089</v>
+        <v>483128</v>
       </c>
       <c r="R7" t="n">
-        <v>6844992</v>
+        <v>6845017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134349278</v>
+        <v>134348872</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483128</v>
+        <v>483089</v>
       </c>
       <c r="R8" t="n">
-        <v>6845017</v>
+        <v>6844992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
         <v>134349817</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>134348662</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134349250</v>
+        <v>134349215</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,20 +1585,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483121</v>
+        <v>483108</v>
       </c>
       <c r="R11" t="n">
-        <v>6845025</v>
+        <v>6845021</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1654,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134349215</v>
+        <v>134349250</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,29 +1691,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483108</v>
+        <v>483121</v>
       </c>
       <c r="R12" t="n">
-        <v>6845021</v>
+        <v>6845025</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>134350436</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>134349652</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,32 +1954,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134348728</v>
+        <v>134349116</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483141</v>
+        <v>483079</v>
       </c>
       <c r="R15" t="n">
-        <v>6844968</v>
+        <v>6844999</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2025,11 +2025,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2056,32 +2051,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134349116</v>
+        <v>134348728</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,13 +2086,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483079</v>
+        <v>483141</v>
       </c>
       <c r="R16" t="n">
-        <v>6844999</v>
+        <v>6844968</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,6 +2122,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2156,7 +2156,7 @@
         <v>134349621</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>134349703</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>134349000</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>134349419</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>134349302</v>
       </c>
       <c r="B23" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>134349101</v>
       </c>
       <c r="B24" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51121-2022 artfynd.xlsx
+++ b/artfynd/A 51121-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134349539</v>
+        <v>134349419</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483155</v>
+        <v>483136</v>
       </c>
       <c r="R2" t="n">
-        <v>6845008</v>
+        <v>6844988</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134349187</v>
+        <v>134349703</v>
       </c>
       <c r="B3" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483105</v>
+        <v>483195</v>
       </c>
       <c r="R3" t="n">
-        <v>6845012</v>
+        <v>6844994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134349616</v>
+        <v>134349817</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483159</v>
+        <v>483198</v>
       </c>
       <c r="R4" t="n">
-        <v>6844996</v>
+        <v>6845004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134350051</v>
+        <v>134349953</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1010,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483213</v>
+        <v>483203</v>
       </c>
       <c r="R5" t="n">
-        <v>6844994</v>
+        <v>6844991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134349953</v>
+        <v>134350051</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483203</v>
+        <v>483213</v>
       </c>
       <c r="R6" t="n">
-        <v>6844991</v>
+        <v>6844994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134349278</v>
+        <v>134350436</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483128</v>
+        <v>483188</v>
       </c>
       <c r="R7" t="n">
-        <v>6845017</v>
+        <v>6844940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134348872</v>
+        <v>134348728</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483089</v>
+        <v>483141</v>
       </c>
       <c r="R8" t="n">
-        <v>6844992</v>
+        <v>6844968</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1337,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1363,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134349817</v>
+        <v>134350525</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483198</v>
+        <v>483195</v>
       </c>
       <c r="R9" t="n">
-        <v>6845004</v>
+        <v>6844877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,45 +1461,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134348662</v>
+        <v>134349429</v>
       </c>
       <c r="B10" t="n">
-        <v>99188</v>
+        <v>58107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483223</v>
+        <v>483134</v>
       </c>
       <c r="R10" t="n">
-        <v>6844974</v>
+        <v>6844986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134349215</v>
+        <v>134348662</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,26 +1591,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483108</v>
+        <v>483223</v>
       </c>
       <c r="R11" t="n">
-        <v>6845021</v>
+        <v>6844974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134349250</v>
+        <v>134348872</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483121</v>
+        <v>483089</v>
       </c>
       <c r="R12" t="n">
-        <v>6845025</v>
+        <v>6844992</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1760,45 +1757,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134350436</v>
+        <v>134349000</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483188</v>
+        <v>483071</v>
       </c>
       <c r="R13" t="n">
-        <v>6844940</v>
+        <v>6844997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134349652</v>
+        <v>134349101</v>
       </c>
       <c r="B14" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,17 +1891,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483161</v>
+        <v>483077</v>
       </c>
       <c r="R14" t="n">
-        <v>6844985</v>
+        <v>6844998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1972,7 @@
         <v>134349116</v>
       </c>
       <c r="B15" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,48 +2066,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134348728</v>
+        <v>134349187</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483141</v>
+        <v>483105</v>
       </c>
       <c r="R16" t="n">
-        <v>6844968</v>
+        <v>6845012</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,11 +2146,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2153,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134349621</v>
+        <v>134349215</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,17 +2200,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483156</v>
+        <v>483108</v>
       </c>
       <c r="R17" t="n">
-        <v>6844997</v>
+        <v>6845021</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2250,53 +2278,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134349429</v>
+        <v>134349250</v>
       </c>
       <c r="B18" t="n">
-        <v>58107</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205976</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483134</v>
+        <v>483121</v>
       </c>
       <c r="R18" t="n">
-        <v>6844986</v>
+        <v>6845025</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2352,32 +2375,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134349703</v>
+        <v>134349278</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2387,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483195</v>
+        <v>483128</v>
       </c>
       <c r="R19" t="n">
-        <v>6844994</v>
+        <v>6845017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,48 +2472,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134350525</v>
+        <v>134349302</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483195</v>
+        <v>483126</v>
       </c>
       <c r="R20" t="n">
-        <v>6844877</v>
+        <v>6845005</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2520,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2551,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134349000</v>
+        <v>134349539</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2579,26 +2606,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483071</v>
+        <v>483155</v>
       </c>
       <c r="R21" t="n">
-        <v>6844997</v>
+        <v>6845008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134349419</v>
+        <v>134349616</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2692,13 +2710,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483136</v>
+        <v>483159</v>
       </c>
       <c r="R22" t="n">
-        <v>6844988</v>
+        <v>6844996</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2754,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134349302</v>
+        <v>134349621</v>
       </c>
       <c r="B23" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2782,29 +2800,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483126</v>
+        <v>483156</v>
       </c>
       <c r="R23" t="n">
-        <v>6845005</v>
+        <v>6844997</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2860,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134349101</v>
+        <v>134349652</v>
       </c>
       <c r="B24" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,26 +2897,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölsjöån, Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483077</v>
+        <v>483161</v>
       </c>
       <c r="R24" t="n">
-        <v>6844998</v>
+        <v>6844985</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 51121-2022 artfynd.xlsx
+++ b/artfynd/A 51121-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349817</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349953</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134350051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134350436</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348728</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134350525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349429</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348662</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348872</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349101</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349116</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349187</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2275,6 +2355,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349215</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2372,6 +2457,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2469,6 +2559,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349278</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349302</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349539</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349616</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349621</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,8 +3078,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134349652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>